--- a/public/templates/office/EMP_DEG_080_데이터베이스명세서.xlsx
+++ b/public/templates/office/EMP_DEG_080_데이터베이스명세서.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="C12" s="112" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="140" t="n"/>
@@ -2397,13 +2397,13 @@
     <row r="22" ht="21" customHeight="1" s="139">
       <c r="C22" s="143" t="inlineStr">
         <is>
-          <t>그로브소프트 (EMPASY)</t>
+          <t>엠파시 (EMPASY)</t>
         </is>
       </c>
       <c r="D22" s="144" t="n"/>
       <c r="E22" s="145" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한빛글로벌</t>
         </is>
       </c>
       <c r="F22" s="146" t="n"/>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="F4" s="61" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한빛글로벌</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       <c r="I6" s="14" t="n"/>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>심의신청번호(CLM-YYYYMMDD-XXXX)</t>
+          <t>심의신청번호(CLM-YYYYMMDD-0001)</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
       <c r="I7" s="14" t="n"/>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>티움넷(MarketingHub) 연동 신청번호</t>
+          <t>마케팅허브(MarketingHub) 연동 신청번호</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       <c r="F4" s="50" t="n"/>
       <c r="G4" s="80" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="H4" s="1" t="n"/>
@@ -5545,7 +5545,7 @@
       <c r="F5" s="50" t="n"/>
       <c r="G5" s="81" t="inlineStr">
         <is>
-          <t>오병문 AA</t>
+          <t>박준혁 AA</t>
         </is>
       </c>
       <c r="H5" s="1" t="n"/>
@@ -8897,7 +8897,7 @@
       <c r="F4" s="50" t="n"/>
       <c r="G4" s="80" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="H4" s="1" t="n"/>
@@ -8943,7 +8943,7 @@
       <c r="F5" s="50" t="n"/>
       <c r="G5" s="81" t="inlineStr">
         <is>
-          <t>오병문 AA</t>
+          <t>박준혁 AA</t>
         </is>
       </c>
       <c r="H5" s="1" t="n"/>
@@ -10040,7 +10040,7 @@
       <c r="F4" s="50" t="n"/>
       <c r="G4" s="80" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="H4" s="1" t="n"/>
@@ -10087,7 +10087,7 @@
       <c r="F5" s="50" t="n"/>
       <c r="G5" s="81" t="inlineStr">
         <is>
-          <t>오병문 AA</t>
+          <t>박준혁 AA</t>
         </is>
       </c>
       <c r="H5" s="1" t="n"/>

--- a/public/templates/office/EMP_DEG_080_데이터베이스명세서.xlsx
+++ b/public/templates/office/EMP_DEG_080_데이터베이스명세서.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="C12" s="112" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="140" t="n"/>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D4" s="59" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 구축 기준 상세 작성</t>
+          <t>SyncFlow AI 시스템 구축 기준 상세 작성</t>
         </is>
       </c>
       <c r="E4" s="60" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D5" s="64" t="inlineStr">
         <is>
-          <t>review_request 심의상태(QUEUED, FAILED) 확장 및 PostgreSQL pgvector 1536차원(VECTOR(1536)) HNSW 벡터 인덱스 일원화 반영</t>
+          <t>verify_request 검증상태(QUEUED, FAILED) 확장 및 PostgreSQL pgvector 1536차원(VECTOR(1536)) HNSW 벡터 인덱스 일원화 반영</t>
         </is>
       </c>
       <c r="E5" s="65" t="inlineStr">
@@ -2796,12 +2796,12 @@
     <row r="5">
       <c r="A5" s="28" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="B5" s="29" t="inlineStr">
         <is>
-          <t>심의요청마스터</t>
+          <t>검증요청마스터</t>
         </is>
       </c>
       <c r="C5" s="30" t="n">
@@ -2839,19 +2839,19 @@
       </c>
       <c r="J5" s="33" t="inlineStr">
         <is>
-          <t>심의요청 고유식별자(PK)</t>
+          <t>검증요청 고유식별자(PK)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="28" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>심의요청마스터</t>
+          <t>검증요청마스터</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
@@ -2881,19 +2881,19 @@
       <c r="I6" s="14" t="n"/>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>심의신청번호(CLM-YYYYMMDD-0001)</t>
+          <t>검증신청번호(REV-YYYYMMDD-0001)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="28" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>심의요청마스터</t>
+          <t>검증요청마스터</t>
         </is>
       </c>
       <c r="C7" s="30" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>mkthub_req_no</t>
+          <t>srm_req_no</t>
         </is>
       </c>
       <c r="E7" s="14" t="n"/>
@@ -2923,19 +2923,19 @@
       <c r="I7" s="14" t="n"/>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>마케팅허브(MarketingHub) 연동 신청번호</t>
+          <t>전자구매포털(SRM-Portal) 연동 신청번호</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="28" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>심의요청마스터</t>
+          <t>검증요청마스터</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
@@ -2965,19 +2965,19 @@
       <c r="I8" s="14" t="n"/>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t>브랜드코드</t>
+          <t>사업본부코드</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="28" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="B9" s="29" t="inlineStr">
         <is>
-          <t>심의요청마스터</t>
+          <t>검증요청마스터</t>
         </is>
       </c>
       <c r="C9" s="30" t="n">
@@ -3007,19 +3007,19 @@
       <c r="I9" s="14" t="n"/>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>제품/처방코드(ProductLab 연동키)</t>
+          <t>제품/설계사양코드(PLM-Nexus 연동키)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="28" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="B10" s="29" t="inlineStr">
         <is>
-          <t>심의요청마스터</t>
+          <t>검증요청마스터</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
@@ -3056,12 +3056,12 @@
     <row r="11">
       <c r="A11" s="28" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>심의요청마스터</t>
+          <t>검증요청마스터</t>
         </is>
       </c>
       <c r="C11" s="30" t="n">
@@ -3091,19 +3091,19 @@
       <c r="I11" s="14" t="n"/>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>매체구분(PPTX/PDF/JPG/VIDEO_MP4)</t>
+          <t>매체구분(PPTX/PDF/JPG/VIDEO_CAD/PDF)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="28" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>심의요청마스터</t>
+          <t>검증요청마스터</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
@@ -3137,19 +3137,19 @@
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t>심의상태(DRAFT/REQUESTED/QUEUED/ANALYZING/FAILED/IN_REVIEW/REJECTED/CONFIRMED)</t>
+          <t>검증상태(DRAFT/REQUESTED/QUEUED/ANALYZING/FAILED/IN_REVIEW/REJECTED/CONFIRMED)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="28" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="B13" s="29" t="inlineStr">
         <is>
-          <t>심의요청마스터</t>
+          <t>검증요청마스터</t>
         </is>
       </c>
       <c r="C13" s="30" t="n">
@@ -3186,12 +3186,12 @@
     <row r="14">
       <c r="A14" s="28" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>심의요청마스터</t>
+          <t>검증요청마스터</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
@@ -3228,12 +3228,12 @@
     <row r="15">
       <c r="A15" s="28" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>심의요청마스터</t>
+          <t>검증요청마스터</t>
         </is>
       </c>
       <c r="C15" s="30" t="n">
@@ -3267,19 +3267,19 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>심의요청 등록일시</t>
+          <t>검증요청 등록일시</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="28" t="inlineStr">
         <is>
-          <t>review_document</t>
+          <t>verify_document</t>
         </is>
       </c>
       <c r="B16" s="29" t="inlineStr">
         <is>
-          <t>심의시안파일</t>
+          <t>검증계약·도서파일</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
@@ -3317,19 +3317,19 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>시안파일 고유식별자(PK)</t>
+          <t>계약·도서파일 고유식별자(PK)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="28" t="inlineStr">
         <is>
-          <t>review_document</t>
+          <t>verify_document</t>
         </is>
       </c>
       <c r="B17" s="29" t="inlineStr">
         <is>
-          <t>심의시안파일</t>
+          <t>검증계약·도서파일</t>
         </is>
       </c>
       <c r="C17" s="30" t="n">
@@ -3359,19 +3359,19 @@
       <c r="I17" s="14" t="n"/>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>심의요청 ID(FK)</t>
+          <t>검증요청 ID(FK)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="28" t="inlineStr">
         <is>
-          <t>review_document</t>
+          <t>verify_document</t>
         </is>
       </c>
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>심의시안파일</t>
+          <t>검증계약·도서파일</t>
         </is>
       </c>
       <c r="C18" s="14" t="n">
@@ -3408,12 +3408,12 @@
     <row r="19">
       <c r="A19" s="28" t="inlineStr">
         <is>
-          <t>review_document</t>
+          <t>verify_document</t>
         </is>
       </c>
       <c r="B19" s="29" t="inlineStr">
         <is>
-          <t>심의시안파일</t>
+          <t>검증계약·도서파일</t>
         </is>
       </c>
       <c r="C19" s="30" t="n">
@@ -3450,12 +3450,12 @@
     <row r="20">
       <c r="A20" s="28" t="inlineStr">
         <is>
-          <t>review_document</t>
+          <t>verify_document</t>
         </is>
       </c>
       <c r="B20" s="29" t="inlineStr">
         <is>
-          <t>심의시안파일</t>
+          <t>검증계약·도서파일</t>
         </is>
       </c>
       <c r="C20" s="14" t="n">
@@ -3492,12 +3492,12 @@
     <row r="21">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>review_video_snapshot</t>
+          <t>verify_video_snapshot</t>
         </is>
       </c>
       <c r="B21" s="29" t="inlineStr">
         <is>
-          <t>동영상지정캡처장면</t>
+          <t>설계도면지정스냅샷장면</t>
         </is>
       </c>
       <c r="C21" s="30" t="n">
@@ -3535,19 +3535,19 @@
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>캡처 장면 고유식별자(PK)</t>
+          <t>도면 스냅샷 고유식별자(PK)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>review_video_snapshot</t>
+          <t>verify_video_snapshot</t>
         </is>
       </c>
       <c r="B22" s="29" t="inlineStr">
         <is>
-          <t>동영상지정캡처장면</t>
+          <t>설계도면지정스냅샷장면</t>
         </is>
       </c>
       <c r="C22" s="14" t="n">
@@ -3577,19 +3577,19 @@
       <c r="I22" s="78" t="n"/>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>동영상 파일 ID(FK)</t>
+          <t>설계도면 파일 ID(FK)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>review_video_snapshot</t>
+          <t>verify_video_snapshot</t>
         </is>
       </c>
       <c r="B23" s="29" t="inlineStr">
         <is>
-          <t>동영상지정캡처장면</t>
+          <t>설계도면지정스냅샷장면</t>
         </is>
       </c>
       <c r="C23" s="30" t="n">
@@ -3630,12 +3630,12 @@
     <row r="24">
       <c r="A24" s="28" t="inlineStr">
         <is>
-          <t>review_video_snapshot</t>
+          <t>verify_video_snapshot</t>
         </is>
       </c>
       <c r="B24" s="29" t="inlineStr">
         <is>
-          <t>동영상지정캡처장면</t>
+          <t>설계도면지정스냅샷장면</t>
         </is>
       </c>
       <c r="C24" s="14" t="n">
@@ -3676,12 +3676,12 @@
     <row r="25">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>review_video_snapshot</t>
+          <t>verify_video_snapshot</t>
         </is>
       </c>
       <c r="B25" s="29" t="inlineStr">
         <is>
-          <t>동영상지정캡처장면</t>
+          <t>설계도면지정스냅샷장면</t>
         </is>
       </c>
       <c r="C25" s="30" t="n">
@@ -3711,19 +3711,19 @@
       <c r="I25" s="14" t="n"/>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>캡처 장면 이미지 S3 오브젝트 키</t>
+          <t>도면 스냅샷 이미지 S3 오브젝트 키</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>review_video_snapshot</t>
+          <t>verify_video_snapshot</t>
         </is>
       </c>
       <c r="B26" s="29" t="inlineStr">
         <is>
-          <t>동영상지정캡처장면</t>
+          <t>설계도면지정스냅샷장면</t>
         </is>
       </c>
       <c r="C26" s="14" t="n">
@@ -3757,19 +3757,19 @@
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>장면 이미지 OCR/심의 처리 상태</t>
+          <t>장면 이미지 OCR/검증 처리 상태</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>review_sentence</t>
+          <t>verify_sentence</t>
         </is>
       </c>
       <c r="B27" s="29" t="inlineStr">
         <is>
-          <t>심의추출문장</t>
+          <t>검증추출문장</t>
         </is>
       </c>
       <c r="C27" s="30" t="n">
@@ -3807,19 +3807,19 @@
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>심의문장 고유식별자(PK)</t>
+          <t>검증문장 고유식별자(PK)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>review_sentence</t>
+          <t>verify_sentence</t>
         </is>
       </c>
       <c r="B28" s="29" t="inlineStr">
         <is>
-          <t>심의추출문장</t>
+          <t>검증추출문장</t>
         </is>
       </c>
       <c r="C28" s="14" t="n">
@@ -3849,19 +3849,19 @@
       <c r="I28" s="14" t="n"/>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>심의요청 ID(FK)</t>
+          <t>검증요청 ID(FK)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>review_sentence</t>
+          <t>verify_sentence</t>
         </is>
       </c>
       <c r="B29" s="29" t="inlineStr">
         <is>
-          <t>심의추출문장</t>
+          <t>검증추출문장</t>
         </is>
       </c>
       <c r="C29" s="30" t="n">
@@ -3891,19 +3891,19 @@
       <c r="I29" s="14" t="n"/>
       <c r="J29" s="17" t="inlineStr">
         <is>
-          <t>슬라이드/동영상 캡처장면 ID(FK)</t>
+          <t>슬라이드/동도면 스냅샷장면 ID(FK)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="28" t="inlineStr">
         <is>
-          <t>review_sentence</t>
+          <t>verify_sentence</t>
         </is>
       </c>
       <c r="B30" s="29" t="inlineStr">
         <is>
-          <t>심의추출문장</t>
+          <t>검증추출문장</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
@@ -3944,12 +3944,12 @@
     <row r="31">
       <c r="A31" s="28" t="inlineStr">
         <is>
-          <t>review_sentence</t>
+          <t>verify_sentence</t>
         </is>
       </c>
       <c r="B31" s="29" t="inlineStr">
         <is>
-          <t>심의추출문장</t>
+          <t>검증추출문장</t>
         </is>
       </c>
       <c r="C31" s="30" t="n">
@@ -3986,12 +3986,12 @@
     <row r="32">
       <c r="A32" s="28" t="inlineStr">
         <is>
-          <t>review_sentence</t>
+          <t>verify_sentence</t>
         </is>
       </c>
       <c r="B32" s="29" t="inlineStr">
         <is>
-          <t>심의추출문장</t>
+          <t>검증추출문장</t>
         </is>
       </c>
       <c r="C32" s="14" t="n">
@@ -4021,19 +4021,19 @@
       <c r="I32" s="14" t="n"/>
       <c r="J32" s="17" t="inlineStr">
         <is>
-          <t>시안/장면 내 바운딩박스 상대좌표(%)</t>
+          <t>계약·도서/장면 내 바운딩박스 상대좌표(%)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="28" t="inlineStr">
         <is>
-          <t>review_sentence</t>
+          <t>verify_sentence</t>
         </is>
       </c>
       <c r="B33" s="29" t="inlineStr">
         <is>
-          <t>심의추출문장</t>
+          <t>검증추출문장</t>
         </is>
       </c>
       <c r="C33" s="30" t="n">
@@ -4074,7 +4074,7 @@
     <row r="34" customFormat="1" s="8">
       <c r="A34" s="28" t="inlineStr">
         <is>
-          <t>syncguard_ai_analysis</t>
+          <t>syncflow_ai_analysis</t>
         </is>
       </c>
       <c r="B34" s="29" t="inlineStr">
@@ -4124,7 +4124,7 @@
     <row r="35">
       <c r="A35" s="28" t="inlineStr">
         <is>
-          <t>syncguard_ai_analysis</t>
+          <t>syncflow_ai_analysis</t>
         </is>
       </c>
       <c r="B35" s="29" t="inlineStr">
@@ -4159,14 +4159,14 @@
       <c r="I35" s="14" t="n"/>
       <c r="J35" s="17" t="inlineStr">
         <is>
-          <t>심의문장 ID(FK)</t>
+          <t>검증문장 ID(FK)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="28" t="inlineStr">
         <is>
-          <t>syncguard_ai_analysis</t>
+          <t>syncflow_ai_analysis</t>
         </is>
       </c>
       <c r="B36" s="29" t="inlineStr">
@@ -4208,7 +4208,7 @@
     <row r="37" customFormat="1" s="8">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>syncguard_ai_analysis</t>
+          <t>syncflow_ai_analysis</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
@@ -4243,14 +4243,14 @@
       <c r="I37" s="20" t="n"/>
       <c r="J37" s="17" t="inlineStr">
         <is>
-          <t>1단계 표현사전/전성분 룰 매칭 내역</t>
+          <t>1단계 표현사전/자재BOM 룰 매칭 내역</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>syncguard_ai_analysis</t>
+          <t>syncflow_ai_analysis</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
@@ -4285,14 +4285,14 @@
       <c r="I38" s="78" t="n"/>
       <c r="J38" s="17" t="inlineStr">
         <is>
-          <t>2단계 식약처 법령·ProductLab 실증 근거</t>
+          <t>2단계 공정위·표준원 법령·PLM-Nexus 시험검증 근거</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>syncguard_ai_analysis</t>
+          <t>syncflow_ai_analysis</t>
         </is>
       </c>
       <c r="B39" s="19" t="inlineStr">
@@ -4327,19 +4327,19 @@
       <c r="I39" s="14" t="n"/>
       <c r="J39" s="17" t="inlineStr">
         <is>
-          <t>3단계 법적 안전 대체문안 추천 목록</t>
+          <t>3단계 법적 안전 표준수정조항 추천 목록</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>review_ra_review</t>
+          <t>verify_ra_review</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>RA최종심의</t>
+          <t>QA최종검증</t>
         </is>
       </c>
       <c r="C40" s="14" t="n">
@@ -4377,19 +4377,19 @@
       </c>
       <c r="J40" s="17" t="inlineStr">
         <is>
-          <t>RA심의 고유식별자(PK)</t>
+          <t>QA검증 고유식별자(PK)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>review_ra_review</t>
+          <t>verify_ra_review</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>RA최종심의</t>
+          <t>QA최종검증</t>
         </is>
       </c>
       <c r="C41" s="14" t="n">
@@ -4419,19 +4419,19 @@
       <c r="I41" s="14" t="n"/>
       <c r="J41" s="17" t="inlineStr">
         <is>
-          <t>심의문장 ID(FK)</t>
+          <t>검증문장 ID(FK)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>review_ra_review</t>
+          <t>verify_ra_review</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
-          <t>RA최종심의</t>
+          <t>QA최종검증</t>
         </is>
       </c>
       <c r="C42" s="14" t="n">
@@ -4461,19 +4461,19 @@
       <c r="I42" s="14" t="n"/>
       <c r="J42" s="17" t="inlineStr">
         <is>
-          <t>RA 최종 확정 등급(오버라이드 포함)</t>
+          <t>QA 최종 확정 등급(오버라이드 포함)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>review_ra_review</t>
+          <t>verify_ra_review</t>
         </is>
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>RA최종심의</t>
+          <t>QA최종검증</t>
         </is>
       </c>
       <c r="C43" s="14" t="n">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>confirmed_claim</t>
+          <t>confirmed_Spec</t>
         </is>
       </c>
       <c r="E43" s="14" t="n"/>
@@ -4503,19 +4503,19 @@
       <c r="I43" s="78" t="n"/>
       <c r="J43" s="17" t="inlineStr">
         <is>
-          <t>RA 최종 채택/수정 문안</t>
+          <t>QA 최종 채택/수정 계약조항</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>review_ra_review</t>
+          <t>verify_ra_review</t>
         </is>
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>RA최종심의</t>
+          <t>QA최종검증</t>
         </is>
       </c>
       <c r="C44" s="14" t="n">
@@ -4545,19 +4545,19 @@
       <c r="I44" s="14" t="n"/>
       <c r="J44" s="17" t="inlineStr">
         <is>
-          <t>RA 심의담당자 사번</t>
+          <t>QA 검증담당자 사번</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="18" t="inlineStr">
         <is>
-          <t>review_evidence</t>
+          <t>verify_evidence</t>
         </is>
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>실증자료매핑</t>
+          <t>시험성적서매핑</t>
         </is>
       </c>
       <c r="C45" s="14" t="n">
@@ -4595,19 +4595,19 @@
       </c>
       <c r="J45" s="17" t="inlineStr">
         <is>
-          <t>실증자료 고유식별자(PK)</t>
+          <t>시험성적서 고유식별자(PK)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>review_evidence</t>
+          <t>verify_evidence</t>
         </is>
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>실증자료매핑</t>
+          <t>시험성적서매핑</t>
         </is>
       </c>
       <c r="C46" s="14" t="n">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>productlab_cert_no</t>
+          <t>plmnexus_cert_no</t>
         </is>
       </c>
       <c r="E46" s="14" t="n"/>
@@ -4637,19 +4637,19 @@
       <c r="I46" s="14" t="n"/>
       <c r="J46" s="17" t="inlineStr">
         <is>
-          <t>ProductLab 인체적용시험/보고서 번호</t>
+          <t>PLM-Nexus 공인신뢰성시험/보고서 번호</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="18" t="inlineStr">
         <is>
-          <t>review_evidence</t>
+          <t>verify_evidence</t>
         </is>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
-          <t>실증자료매핑</t>
+          <t>시험성적서매핑</t>
         </is>
       </c>
       <c r="C47" s="14" t="n">
@@ -4679,14 +4679,14 @@
       <c r="I47" s="78" t="n"/>
       <c r="J47" s="17" t="inlineStr">
         <is>
-          <t>시험기관명 및 피험자수/기간 메타</t>
+          <t>시험기관명 및 시험시료수/기간 메타</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>review_rule_dict</t>
+          <t>verify_rule_dict</t>
         </is>
       </c>
       <c r="B48" s="19" t="inlineStr">
@@ -4736,7 +4736,7 @@
     <row r="49">
       <c r="A49" s="18" t="inlineStr">
         <is>
-          <t>review_rule_dict</t>
+          <t>verify_rule_dict</t>
         </is>
       </c>
       <c r="B49" s="19" t="inlineStr">
@@ -4771,14 +4771,14 @@
       <c r="I49" s="14" t="n"/>
       <c r="J49" s="17" t="inlineStr">
         <is>
-          <t>위반유형(의약품오인/실증필요/기능성 등)</t>
+          <t>위반유형(불공정독소조항/성적서필요/핵심규격 등)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>review_rule_dict</t>
+          <t>verify_rule_dict</t>
         </is>
       </c>
       <c r="B50" s="19" t="inlineStr">
@@ -4820,12 +4820,12 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>review_precedent</t>
+          <t>verify_precedent</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>법령및처분사례벡터</t>
+          <t>법령및심결사례벡터</t>
         </is>
       </c>
       <c r="C51" s="14" t="n">
@@ -4863,19 +4863,19 @@
       </c>
       <c r="J51" s="17" t="inlineStr">
         <is>
-          <t>법령/처분사례 청크 ID(PK)</t>
+          <t>법령/심결사례 청크 ID(PK)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="17.25" customHeight="1" s="139" thickBot="1">
       <c r="A52" s="23" t="inlineStr">
         <is>
-          <t>review_precedent</t>
+          <t>verify_precedent</t>
         </is>
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>법령및처분사례벡터</t>
+          <t>법령및심결사례벡터</t>
         </is>
       </c>
       <c r="C52" s="25" t="n">
@@ -5083,12 +5083,12 @@
     <row r="5">
       <c r="A5" s="151" t="inlineStr">
         <is>
-          <t>pk_review_request</t>
+          <t>pk_verify_request</t>
         </is>
       </c>
       <c r="B5" s="151" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="C5" s="152" t="n">
@@ -5114,12 +5114,12 @@
     <row r="6">
       <c r="A6" s="151" t="inlineStr">
         <is>
-          <t>idx_review_request_status</t>
+          <t>idx_verify_request_status</t>
         </is>
       </c>
       <c r="B6" s="151" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="C6" s="152" t="n">
@@ -5138,19 +5138,19 @@
       <c r="F6" s="14" t="n"/>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>심의 상태 및 요청일자별 목록 조회 최적화</t>
+          <t>검증 상태 및 요청일자별 목록 조회 최적화</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="151" t="inlineStr">
         <is>
-          <t>idx_review_request_brand</t>
+          <t>idx_verify_request_brand</t>
         </is>
       </c>
       <c r="B7" s="151" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="C7" s="152" t="n">
@@ -5173,19 +5173,19 @@
       </c>
       <c r="G7" s="33" t="inlineStr">
         <is>
-          <t>브랜드코드별 심의 이력 필터링 인덱스</t>
+          <t>사업본부코드별 검증 이력 필터링 인덱스</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="151" t="inlineStr">
         <is>
-          <t>pk_review_sentence</t>
+          <t>pk_verify_sentence</t>
         </is>
       </c>
       <c r="B8" s="151" t="inlineStr">
         <is>
-          <t>review_sentence</t>
+          <t>verify_sentence</t>
         </is>
       </c>
       <c r="C8" s="152" t="n">
@@ -5204,19 +5204,19 @@
       <c r="F8" s="14" t="n"/>
       <c r="G8" s="154" t="inlineStr">
         <is>
-          <t>심의 추출 문장 Primary Key / 요청별 문장 순서 인덱스</t>
+          <t>검증 추출 문장 Primary Key / 요청별 문장 순서 인덱스</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="151" t="inlineStr">
         <is>
-          <t>idx_review_sentence_req</t>
+          <t>idx_verify_sentence_req</t>
         </is>
       </c>
       <c r="B9" s="151" t="inlineStr">
         <is>
-          <t>review_sentence</t>
+          <t>verify_sentence</t>
         </is>
       </c>
       <c r="C9" s="152" t="n">
@@ -5238,12 +5238,12 @@
     <row r="10">
       <c r="A10" s="151" t="inlineStr">
         <is>
-          <t>pk_review_rule</t>
+          <t>pk_verify_rule</t>
         </is>
       </c>
       <c r="B10" s="151" t="inlineStr">
         <is>
-          <t>review_rule</t>
+          <t>verify_rule</t>
         </is>
       </c>
       <c r="C10" s="152" t="n">
@@ -5269,12 +5269,12 @@
     <row r="11" ht="17.25" customHeight="1" s="139" thickBot="1">
       <c r="A11" s="151" t="inlineStr">
         <is>
-          <t>idx_review_rule_cat</t>
+          <t>idx_verify_rule_cat</t>
         </is>
       </c>
       <c r="B11" s="151" t="inlineStr">
         <is>
-          <t>review_rule</t>
+          <t>verify_rule</t>
         </is>
       </c>
       <c r="C11" s="152" t="n">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="B12" s="156" t="inlineStr">
         <is>
-          <t>review_precedent</t>
+          <t>verify_precedent</t>
         </is>
       </c>
       <c r="C12" s="157" t="n">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B4" s="159" t="inlineStr">
         <is>
-          <t>sp_archive_review_history</t>
+          <t>sp_archive_verify_history</t>
         </is>
       </c>
       <c r="C4" s="159" t="inlineStr">
         <is>
-          <t>심의 이력 데이터 아카이빙</t>
+          <t>검증 이력 데이터 아카이빙</t>
         </is>
       </c>
       <c r="D4" s="158" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="E4" s="159" t="inlineStr">
         <is>
-          <t>3년이 경과된 완료 심의 의뢰 건 및 문안 데이터를 이력 보관 파티션 테이블로 이동 보관</t>
+          <t>3년이 경과된 완료 검증 요청 건 및 계약조항 데이터를 이력 보관 파티션 테이블로 이동 보관</t>
         </is>
       </c>
       <c r="F4" s="50" t="n"/>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B4" s="159" t="inlineStr">
         <is>
-          <t>fn_calc_review_risk_score</t>
+          <t>fn_calc_verify_risk_score</t>
         </is>
       </c>
       <c r="C4" s="159" t="inlineStr">
         <is>
-          <t>심의 종합 위험도 점수 계산</t>
+          <t>검증 종합 위험도 점수 계산</t>
         </is>
       </c>
       <c r="D4" s="159" t="inlineStr">
@@ -7744,17 +7744,17 @@
       </c>
       <c r="B4" s="159" t="inlineStr">
         <is>
-          <t>v_review_dashboard</t>
+          <t>v_verify_dashboard</t>
         </is>
       </c>
       <c r="C4" s="159" t="inlineStr">
         <is>
-          <t>review_request, review_sentence</t>
+          <t>verify_request, verify_sentence</t>
         </is>
       </c>
       <c r="D4" s="159" t="inlineStr">
         <is>
-          <t>마케터 및 RA 대시보드용 실시간 심의 요약(의뢰번호, 브랜드, 제품명, 위험도, 상태, 경과시간) 조회</t>
+          <t>구매담당자 및 QA 대시보드용 실시간 검증 요약(의뢰번호, 사업본부, 제품명, 위험도, 상태, 경과시간) 조회</t>
         </is>
       </c>
       <c r="E4" s="158" t="inlineStr">
@@ -7785,17 +7785,17 @@
       </c>
       <c r="B5" s="159" t="inlineStr">
         <is>
-          <t>v_review_audit_trail</t>
+          <t>v_verify_audit_trail</t>
         </is>
       </c>
       <c r="C5" s="159" t="inlineStr">
         <is>
-          <t>audit_log, review_request</t>
+          <t>audit_log, verify_request</t>
         </is>
       </c>
       <c r="D5" s="159" t="inlineStr">
         <is>
-          <t>식약처 사후 소명 제출용 통합 감사 추적(심의원문, AI판정, RA의견, 전자서명) 뷰</t>
+          <t>공정위·표준원 사후 소명 제출용 통합 감사 추적(검증원문, AI판정, QA의견, 전자서명) 뷰</t>
         </is>
       </c>
       <c r="E5" s="158" t="inlineStr">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="B5" s="159" t="inlineStr">
         <is>
-          <t>trg_review_timestamp</t>
+          <t>trg_verify_timestamp</t>
         </is>
       </c>
       <c r="C5" s="159" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="D5" s="158" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="E5" s="159" t="inlineStr">
         <is>
-          <t>심의 상태 변경 시 승인일시, 반려일시, 완료일시를 시스템 현재 시각으로 자동 갱신</t>
+          <t>검증 상태 변경 시 승인일시, 반려일시, 완료일시를 시스템 현재 시각으로 자동 갱신</t>
         </is>
       </c>
       <c r="F5" s="50" t="n"/>
@@ -10018,23 +10018,23 @@
       </c>
       <c r="B4" s="159" t="inlineStr">
         <is>
-          <t>seq_review_req_no</t>
+          <t>seq_verify_req_no</t>
         </is>
       </c>
       <c r="C4" s="159" t="inlineStr">
         <is>
-          <t>심의신청번호 채번</t>
+          <t>검증신청번호 채번</t>
         </is>
       </c>
       <c r="D4" s="159" t="inlineStr">
         <is>
-          <t>CLM + YYYYMMDD + 4자리 순번 채번
+          <t>REV + YYYYMMDD + 4자리 순번 채번
 Rule: START 1, INCREMENT 1, CACHE 10</t>
         </is>
       </c>
       <c r="E4" s="159" t="inlineStr">
         <is>
-          <t>review_request.req_no</t>
+          <t>verify_request.req_no</t>
         </is>
       </c>
       <c r="F4" s="50" t="n"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="C5" s="159" t="inlineStr">
         <is>
-          <t>실증자료번호 채번</t>
+          <t>시험성적서번호 채번</t>
         </is>
       </c>
       <c r="D5" s="159" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="E5" s="159" t="inlineStr">
         <is>
-          <t>review_evidence.evidence_no</t>
+          <t>verify_evidence.evidence_no</t>
         </is>
       </c>
       <c r="F5" s="50" t="n"/>
